--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484028_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484028_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9573</v>
+        <v>3.6932</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0225</v>
+        <v>4.9829</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0652</v>
+        <v>-1.2897</v>
       </c>
       <c r="G2" t="n">
         <v>3.4203</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0771</v>
+        <v>-0.1871</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3005</v>
+        <v>0.2608</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2235</v>
+        <v>-0.4479</v>
       </c>
       <c r="V2" t="n">
         <v>-0.532</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1207</v>
+        <v>1.6575</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3658</v>
+        <v>1.5099</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2451</v>
+        <v>0.1476</v>
       </c>
       <c r="G3" t="n">
         <v>0.4725</v>
@@ -688,13 +688,13 @@
         <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>0.466</v>
+        <v>0.0028</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3492</v>
+        <v>0.4933</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8832</v>
+        <v>-0.4904</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6032</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1461</v>
+        <v>0.3322</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0671</v>
+        <v>-1.8538</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2133</v>
+        <v>2.1859</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9177</v>
+        <v>0.2277</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8566</v>
+        <v>0.6851</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0612</v>
+        <v>-0.4573</v>
       </c>
       <c r="J4" t="n">
-        <v>1.787</v>
+        <v>-0.9522</v>
       </c>
       <c r="K4" t="n">
-        <v>1.024</v>
+        <v>0.3279</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7631</v>
+        <v>-1.2801</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1307</v>
+        <v>1.1799</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1674</v>
+        <v>0.3572</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2981</v>
+        <v>0.8227</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.579</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5255</v>
+        <v>-0.5583</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1135</v>
+        <v>-0.1757</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6389</v>
+        <v>-0.3827</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1425</v>
+        <v>0.266</v>
       </c>
       <c r="W4" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.1425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1219</v>
+        <v>0.2762</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3639</v>
+        <v>-1.9651</v>
       </c>
       <c r="F5" t="n">
-        <v>2.242</v>
+        <v>2.2413</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2277</v>
+        <v>1.9177</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6851</v>
+        <v>0.8566</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4573</v>
+        <v>1.0612</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9522</v>
+        <v>1.787</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3279</v>
+        <v>1.024</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2801</v>
+        <v>0.7631</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1799</v>
+        <v>0.1307</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3572</v>
+        <v>-0.1674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8227</v>
+        <v>0.2981</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0124</v>
+        <v>-0.3954</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6858</v>
+        <v>0.2155</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3266</v>
+        <v>-0.6109</v>
       </c>
       <c r="V5" t="n">
-        <v>0.266</v>
+        <v>0.1425</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6781</v>
+        <v>-0.2484</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6444</v>
+        <v>0.9194</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9662</v>
+        <v>-1.1678</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6701</v>
+        <v>-2.844</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0452</v>
+        <v>0.0295</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7153</v>
+        <v>-2.8735</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6322</v>
+        <v>-0.3325</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3682</v>
+        <v>0.9476</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0004</v>
+        <v>-1.2801</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0379</v>
+        <v>-2.5115</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.323</v>
+        <v>-0.9181</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2851</v>
+        <v>-1.5935</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2064</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0454</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4171</v>
+        <v>-0.0369</v>
       </c>
       <c r="V6" t="n">
         <v>0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1326</v>
+        <v>-0.5965</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7072</v>
+        <v>-2.3383</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5746</v>
+        <v>1.7418</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4459</v>
+        <v>-1.6701</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3576</v>
+        <v>0.0452</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0883</v>
+        <v>-1.7153</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9408</v>
+        <v>-1.6322</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1051</v>
+        <v>0.3682</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8357</v>
+        <v>-2.0004</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5051</v>
+        <v>-0.0379</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2525</v>
+        <v>-0.323</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2526</v>
+        <v>0.2851</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6263</v>
+        <v>-0.1247</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7369</v>
+        <v>-0.3174</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1106</v>
+        <v>0.1926</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4724</v>
+        <v>0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4724</v>
+        <v>0.6032</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5096</v>
+        <v>-1.783</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0612</v>
+        <v>-2.2173</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4484</v>
+        <v>0.4343</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.844</v>
+        <v>-1.4459</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0295</v>
+        <v>-0.3576</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8735</v>
+        <v>-1.0883</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3325</v>
+        <v>-0.9408</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9476</v>
+        <v>-0.1051</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2801</v>
+        <v>-0.8357</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5115</v>
+        <v>-0.5051</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9181</v>
+        <v>-0.2525</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5935</v>
+        <v>-0.2526</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9838</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q8" t="n">
+        <v>-2.9758</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.2509</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4724</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4724</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.9838</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.2526</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.9352</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.3175</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.2065</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7001</v>
+        <v>-3.0332</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7376</v>
+        <v>-3.2672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0376</v>
+        <v>0.2339</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9965</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1841</v>
+        <v>-0.5172</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8105</v>
+        <v>-0.34</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3736</v>
+        <v>-0.1772</v>
       </c>
       <c r="V9" t="n">
         <v>0.8692</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1013</v>
+        <v>-6.0057</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4484</v>
+        <v>-3.1003</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6529</v>
+        <v>-2.9054</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7374</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2827</v>
+        <v>0.3783</v>
       </c>
       <c r="T10" t="n">
-        <v>0.924</v>
+        <v>0.2721</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3587</v>
+        <v>0.1062</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4724</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.019500000000001</v>
+        <v>-5.707700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.641500000000001</v>
+        <v>-7.3298</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6221</v>
+        <v>1.6219</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6557</v>
@@ -1312,10 +1312,10 @@
         <v>15.8707</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7289</v>
+        <v>-1.4172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3690999999999999</v>
+        <v>0.6808000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-2.098100000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7874</v>
+        <v>4.0399</v>
       </c>
       <c r="E12" t="n">
         <v>1.3525</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4349</v>
+        <v>2.6874</v>
       </c>
       <c r="G12" t="n">
         <v>3.568</v>
@@ -1390,13 +1390,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6535</v>
+        <v>-0.401</v>
       </c>
       <c r="T12" t="n">
         <v>0.1304</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7839</v>
+        <v>-0.5314</v>
       </c>
       <c r="V12" t="n">
         <v>0.6745</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1976</v>
+        <v>3.2971</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0251</v>
+        <v>0.4332</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1725</v>
+        <v>2.8639</v>
       </c>
       <c r="G13" t="n">
         <v>1.4762</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4609</v>
+        <v>-0.3614</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6858</v>
+        <v>-0.2777</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2249</v>
+        <v>-0.0837</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4377</v>
+        <v>2.371</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6142</v>
+        <v>2.7627</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8235</v>
+        <v>-0.3917</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7187</v>
+        <v>1.2641</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4387</v>
+        <v>0.2018</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2801</v>
+        <v>1.0623</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6287</v>
+        <v>2.1757</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9058</v>
+        <v>2.2082</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7229</v>
+        <v>-0.0325</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.91</v>
+        <v>-0.9116</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4671</v>
+        <v>-2.0064</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5572</v>
+        <v>1.0948</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1741</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0831</v>
+        <v>0.2168</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1597</v>
+        <v>0.3005</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0766</v>
+        <v>-0.0837</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1738</v>
+        <v>0.8901</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2704</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1738</v>
+        <v>-1.3803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0369</v>
+        <v>0.9455</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4566</v>
+        <v>-0.0182</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4198</v>
+        <v>0.9637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2641</v>
+        <v>1.7187</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2018</v>
+        <v>0.4387</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0623</v>
+        <v>1.2801</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1757</v>
+        <v>2.6287</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2082</v>
+        <v>1.9058</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0325</v>
+        <v>0.7229</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9116</v>
+        <v>-0.91</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0064</v>
+        <v>-1.4671</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0948</v>
+        <v>0.5572</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1173</v>
+        <v>0.5909</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0056</v>
+        <v>0.5272</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1117</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8901</v>
+        <v>-0.1738</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2704</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3803</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0188</v>
+        <v>0.0641</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6782</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.697</v>
+        <v>-0.001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0493</v>
       </c>
       <c r="H16" t="n">
-        <v>0.025</v>
+        <v>-2.0367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0402</v>
+        <v>1.9874</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0603</v>
+        <v>1.5901</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0202</v>
+        <v>0.3024</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>1.2877</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0049</v>
+        <v>-1.6395</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0049</v>
+        <v>-2.3392</v>
       </c>
       <c r="O16" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.5952</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-2.1822</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5871</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.6178</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.09859999999999999</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.6032</v>
-      </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4361</v>
+        <v>-0.0619</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6643</v>
+        <v>-0.9595</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2282</v>
+        <v>0.8975</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6318</v>
+        <v>-1.5197</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8767</v>
+        <v>-2.5794</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2449</v>
+        <v>1.0598</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.279</v>
+        <v>-1.2932</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3619</v>
+        <v>-2.4629</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0829</v>
+        <v>1.1698</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3528</v>
+        <v>-0.2265</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5148</v>
+        <v>-0.1165</v>
       </c>
       <c r="O17" t="n">
-        <v>0.162</v>
+        <v>-0.11</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1822</v>
+        <v>-0.1984</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3904</v>
+        <v>-0.2891</v>
       </c>
       <c r="T17" t="n">
-        <v>1.797</v>
+        <v>0.0001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4065</v>
+        <v>-0.2892</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.3581</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4461</v>
+        <v>-0.3708</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.445</v>
+        <v>0.2701</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.001</v>
+        <v>-0.6409</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0493</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0367</v>
+        <v>0.025</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9874</v>
+        <v>0.0402</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5901</v>
+        <v>0.0603</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3024</v>
+        <v>0.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2877</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6395</v>
+        <v>0.0049</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3392</v>
+        <v>0.0049</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6997</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1984</v>
+        <v>0.1672</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1189</v>
+        <v>0.2097</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3173</v>
+        <v>-0.0425</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.6032</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" t="n">
-        <v>0.266</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1367</v>
+        <v>-0.7567</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4091</v>
+        <v>-3.001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2724</v>
+        <v>2.2443</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4515</v>
@@ -1936,13 +1936,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3645</v>
+        <v>0.0156</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7991</v>
+        <v>-0.391</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4347</v>
+        <v>0.4066</v>
       </c>
       <c r="V19" t="n">
         <v>0.0921</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1843</v>
+        <v>-1.1222</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0818</v>
+        <v>-1.3785</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8975</v>
+        <v>0.2563</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5197</v>
+        <v>-0.6318</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5794</v>
+        <v>-0.8767</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0598</v>
+        <v>0.2449</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2932</v>
+        <v>-0.279</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4629</v>
+        <v>-0.3619</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1698</v>
+        <v>0.0829</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2265</v>
+        <v>-0.3528</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1165</v>
+        <v>-0.5148</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.11</v>
+        <v>0.162</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4114</v>
+        <v>0.7043</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1222</v>
+        <v>1.0827</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2892</v>
+        <v>-0.3785</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3581</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1738</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2182</v>
+        <v>-2.3865</v>
       </c>
       <c r="E21" t="n">
         <v>-1.1485</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0697</v>
+        <v>-1.238</v>
       </c>
       <c r="G21" t="n">
         <v>0.2157</v>
@@ -2092,13 +2092,13 @@
         <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5453</v>
+        <v>0.3769</v>
       </c>
       <c r="T21" t="n">
         <v>0.1248</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4204</v>
+        <v>0.2521</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7888</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.019400000000001</v>
+        <v>6.019500000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.622099999999999</v>
+        <v>-1.622100000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>7.641500000000002</v>
+        <v>7.641499999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>3.655600000000001</v>
+        <v>3.655600000000002</v>
       </c>
       <c r="H22" t="n">
         <v>-5.769400000000001</v>
@@ -2170,13 +2170,13 @@
         <v>17.8545</v>
       </c>
       <c r="S22" t="n">
-        <v>1.728800000000001</v>
+        <v>1.7287</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0981</v>
+        <v>2.0979</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3692000000000001</v>
+        <v>-0.3693</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3489</v>
@@ -2185,7 +2185,7 @@
         <v>4.1323</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.4811</v>
+        <v>-5.481100000000001</v>
       </c>
     </row>
   </sheetData>
